--- a/etf_holdings/2026-09-09_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:21</t>
+          <t>2026-09-09 00:50:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:21</t>
+          <t>2026-09-09 00:50:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:21</t>
+          <t>2026-09-09 00:50:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:21</t>
+          <t>2026-09-09 00:50:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:21</t>
+          <t>2026-09-09 00:50:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:21</t>
+          <t>2026-09-09 00:50:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:21</t>
+          <t>2026-09-09 00:50:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:21</t>
+          <t>2026-09-09 00:50:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:21</t>
+          <t>2026-09-09 00:50:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:21</t>
+          <t>2026-09-09 00:50:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:21</t>
+          <t>2026-09-09 00:50:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:21</t>
+          <t>2026-09-09 00:50:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:21</t>
+          <t>2026-09-09 00:50:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:21</t>
+          <t>2026-09-09 00:50:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:21</t>
+          <t>2026-09-09 00:50:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:22</t>
+          <t>2026-09-09 00:50:32</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:22</t>
+          <t>2026-09-09 00:50:32</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:22</t>
+          <t>2026-09-09 00:50:32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:22</t>
+          <t>2026-09-09 00:50:32</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:22</t>
+          <t>2026-09-09 00:50:32</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:22</t>
+          <t>2026-09-09 00:50:32</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:22</t>
+          <t>2026-09-09 00:50:32</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:22</t>
+          <t>2026-09-09 00:50:32</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:22</t>
+          <t>2026-09-09 00:50:32</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:22</t>
+          <t>2026-09-09 00:50:32</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:22</t>
+          <t>2026-09-09 00:50:32</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:22</t>
+          <t>2026-09-09 00:50:32</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:22</t>
+          <t>2026-09-09 00:50:32</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:22</t>
+          <t>2026-09-09 00:50:32</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:22</t>
+          <t>2026-09-09 00:50:32</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:23</t>
+          <t>2026-09-09 00:50:33</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:23</t>
+          <t>2026-09-09 00:50:33</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:23</t>
+          <t>2026-09-09 00:50:33</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:23</t>
+          <t>2026-09-09 00:50:33</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:23</t>
+          <t>2026-09-09 00:50:33</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:23</t>
+          <t>2026-09-09 00:50:33</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:23</t>
+          <t>2026-09-09 00:50:33</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:23</t>
+          <t>2026-09-09 00:50:33</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:23</t>
+          <t>2026-09-09 00:50:33</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:23</t>
+          <t>2026-09-09 00:50:33</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:23</t>
+          <t>2026-09-09 00:50:33</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:23</t>
+          <t>2026-09-09 00:50:33</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:23</t>
+          <t>2026-09-09 00:50:33</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:23</t>
+          <t>2026-09-09 00:50:33</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:23</t>
+          <t>2026-09-09 00:50:33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:24</t>
+          <t>2026-09-09 00:50:34</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:24</t>
+          <t>2026-09-09 00:50:34</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:24</t>
+          <t>2026-09-09 00:50:34</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:24</t>
+          <t>2026-09-09 00:50:34</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:24</t>
+          <t>2026-09-09 00:50:34</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:30</t>
+          <t>2026-09-09 01:15:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:30</t>
+          <t>2026-09-09 01:15:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:30</t>
+          <t>2026-09-09 01:15:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:30</t>
+          <t>2026-09-09 01:15:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:30</t>
+          <t>2026-09-09 01:15:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:30</t>
+          <t>2026-09-09 01:15:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:30</t>
+          <t>2026-09-09 01:15:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:30</t>
+          <t>2026-09-09 01:15:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:30</t>
+          <t>2026-09-09 01:15:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:30</t>
+          <t>2026-09-09 01:15:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:30</t>
+          <t>2026-09-09 01:15:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:30</t>
+          <t>2026-09-09 01:15:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:30</t>
+          <t>2026-09-09 01:15:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:30</t>
+          <t>2026-09-09 01:15:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:30</t>
+          <t>2026-09-09 01:15:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:32</t>
+          <t>2026-09-09 01:15:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:32</t>
+          <t>2026-09-09 01:15:59</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:32</t>
+          <t>2026-09-09 01:15:59</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:32</t>
+          <t>2026-09-09 01:15:59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:32</t>
+          <t>2026-09-09 01:15:59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:32</t>
+          <t>2026-09-09 01:15:59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:32</t>
+          <t>2026-09-09 01:15:59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:32</t>
+          <t>2026-09-09 01:15:59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:32</t>
+          <t>2026-09-09 01:15:59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:32</t>
+          <t>2026-09-09 01:15:59</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:32</t>
+          <t>2026-09-09 01:15:59</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:32</t>
+          <t>2026-09-09 01:15:59</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:32</t>
+          <t>2026-09-09 01:15:59</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:32</t>
+          <t>2026-09-09 01:15:59</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:32</t>
+          <t>2026-09-09 01:15:59</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:33</t>
+          <t>2026-09-09 01:16:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:33</t>
+          <t>2026-09-09 01:16:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:33</t>
+          <t>2026-09-09 01:16:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:33</t>
+          <t>2026-09-09 01:16:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:33</t>
+          <t>2026-09-09 01:16:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:33</t>
+          <t>2026-09-09 01:16:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:33</t>
+          <t>2026-09-09 01:16:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:33</t>
+          <t>2026-09-09 01:16:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:33</t>
+          <t>2026-09-09 01:16:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:33</t>
+          <t>2026-09-09 01:16:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:33</t>
+          <t>2026-09-09 01:16:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:33</t>
+          <t>2026-09-09 01:16:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:33</t>
+          <t>2026-09-09 01:16:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:33</t>
+          <t>2026-09-09 01:16:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:33</t>
+          <t>2026-09-09 01:16:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:34</t>
+          <t>2026-09-09 01:16:01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:34</t>
+          <t>2026-09-09 01:16:01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:34</t>
+          <t>2026-09-09 01:16:01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:34</t>
+          <t>2026-09-09 01:16:01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:34</t>
+          <t>2026-09-09 01:16:01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:57</t>
+          <t>2026-09-09 19:33:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.41%2470</t>
+          <t>-0.2%2465</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2470</v>
+        <v>2465</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.14%753,000</t>
+          <t>9.30%753,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.14%</t>
+          <t>9.30%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:57</t>
+          <t>2026-09-09 19:33:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.05%4710</t>
+          <t>-1.8%4625</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.05%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4710</v>
+        <v>4625</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.85%249,000</t>
+          <t>5.86%249,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.85%</t>
+          <t>5.86%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:57</t>
+          <t>2026-09-09 19:33:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-9.96%12520</t>
+          <t>-0.96%12400</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-9.96%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>12520</v>
+        <v>12400</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.49%80,000</t>
+          <t>5.01%80,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.49%</t>
+          <t>5.01%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:57</t>
+          <t>2026-09-09 19:33:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2.43%1805</t>
+          <t>-0.55%1795</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2.43%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1805</v>
+        <v>1795</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.69%404,000</t>
+          <t>3.64%404,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>3.64%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:57</t>
+          <t>2026-09-09 19:33:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-2.82%5340</t>
+          <t>+0.66%5375</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-2.82%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5340</v>
+        <v>5375</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.69%136,000</t>
+          <t>3.63%136,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>3.63%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:57</t>
+          <t>2026-09-09 19:33:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-6.68%2865</t>
+          <t>-0.52%2850</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.68%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2865</v>
+        <v>2850</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.46%228,600</t>
+          <t>3.27%228,600</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.27%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:57</t>
+          <t>2026-09-09 19:33:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+2.71%531</t>
+          <t>-1.51%523</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+2.71%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.80%1,096,000</t>
+          <t>2.91%1,096,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.91%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:57</t>
+          <t>2026-09-09 19:33:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+1.95%235</t>
+          <t>+0.64%236.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+1.95%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>235</v>
+        <v>236.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.75%2,416,000</t>
+          <t>2.84%2,416,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:57</t>
+          <t>2026-09-09 19:33:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.53%954</t>
+          <t>+4.09%993</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+4.09%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>954</v>
+        <v>993</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.64%563,000</t>
+          <t>2.68%563,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.68%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:57</t>
+          <t>2026-09-09 19:33:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2317鴻海精密工業</t>
+          <t>7769鴻勁精密</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-1.76%251.5</t>
+          <t>-3.59%6720</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>-3.59%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>251.5</v>
+        <v>6720</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.43%1,921,000</t>
+          <t>2.54%73,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.54%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1921000</v>
+        <v>73000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:57</t>
+          <t>2026-09-09 19:33:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7769鴻勁精密</t>
+          <t>2317鴻海精密工業</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+6.17%6970</t>
+          <t>+0.2%252</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+6.17%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6970</v>
+        <v>252</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.37%73,000</t>
+          <t>2.41%1,921,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.41%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>73000</v>
+        <v>1921000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:57</t>
+          <t>2026-09-09 19:33:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-3.95%3285</t>
+          <t>+2.89%3380</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.95%</t>
+          <t>+2.89%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3285</v>
+        <v>3380</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.26%134,000</t>
+          <t>2.20%134,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:57</t>
+          <t>2026-09-09 19:33:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2368金像電子（股）公司</t>
+          <t>2344華邦電子</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-4.02%1075</t>
+          <t>-2.66%183</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-4.02%</t>
+          <t>-2.66%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1075</v>
+        <v>183</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.17%393,000</t>
+          <t>2.15%2,293,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>393000</v>
+        <v>2293000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:57</t>
+          <t>2026-09-09 19:33:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2344華邦電子</t>
+          <t>6515穎崴科技</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+4.44%188</t>
+          <t>-5.45%7280</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+4.44%</t>
+          <t>-5.45%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>188</v>
+        <v>7280</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.04%2,293,000</t>
+          <t>2.12%55,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.12%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>2293000</v>
+        <v>55000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:57</t>
+          <t>2026-09-09 19:33:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8299群聯電子</t>
+          <t>2368金像電子（股）公司</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.48%2085</t>
+          <t>+2.33%1100</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>+2.33%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2085</v>
+        <v>1100</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.04%197,000</t>
+          <t>2.11%393,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>197000</v>
+        <v>393000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:59</t>
+          <t>2026-09-09 19:33:09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+5.56%5795</t>
+          <t>-3.11%5615</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+5.56%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5795</v>
+        <v>5615</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.95%72,000</t>
+          <t>2.09%72,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:59</t>
+          <t>2026-09-09 19:33:09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3653健策精密工業</t>
+          <t>8299群聯電子</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.86%5550</t>
+          <t>0%2085</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.86%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5550</v>
+        <v>2085</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.93%69,000</t>
+          <t>2.05%197,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>2.05%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>69000</v>
+        <v>197000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:59</t>
+          <t>2026-09-09 19:33:09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,25 +1541,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6669緯穎科技服務</t>
+          <t>3653健策精密工業</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-6.02%2340</t>
+          <t>+3.78%5760</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-6.02%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2340</v>
+        <v>5760</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.91%155,105</t>
+          <t>1.91%69,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1568,11 +1568,11 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>155105</v>
+        <v>69000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:59</t>
+          <t>2026-09-09 19:33:09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6515穎崴科技</t>
+          <t>6669緯穎科技服務</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+10%7700</t>
+          <t>-0.64%2325</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>7700</v>
+        <v>2325</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.90%55,000</t>
+          <t>1.81%155,105</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>55000</v>
+        <v>155105</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:59</t>
+          <t>2026-09-09 19:33:09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2345智邦科技</t>
+          <t>5274信驊科技</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-6.9%1955</t>
+          <t>-3.2%18605</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1955</v>
+        <v>18605</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.80%174,000</t>
+          <t>1.76%18,300</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>174000</v>
+        <v>18300</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:59</t>
+          <t>2026-09-09 19:33:09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5274信驊科技</t>
+          <t>3443創意電子</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+0.03%19220</t>
+          <t>-0.59%5925</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>19220</v>
+        <v>5925</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.74%18,300</t>
+          <t>1.76%59,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>18300</v>
+        <v>59000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:59</t>
+          <t>2026-09-09 19:33:09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2327國巨</t>
+          <t>2345智邦科技</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-3.74%567</t>
+          <t>+3.07%2015</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-3.74%</t>
+          <t>+3.07%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>567</v>
+        <v>2015</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.73%595,000</t>
+          <t>1.70%174,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>595000</v>
+        <v>174000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:59</t>
+          <t>2026-09-09 19:33:09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3443創意電子</t>
+          <t>2327國巨</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+0.42%5960</t>
+          <t>-0.35%565</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5960</v>
+        <v>565</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.73%59,000</t>
+          <t>1.69%595,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>59000</v>
+        <v>595000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:59</t>
+          <t>2026-09-09 19:33:09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2382廣達電腦</t>
+          <t>2360致茂電子</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-5.61%328</t>
+          <t>+3.09%2335</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5.61%</t>
+          <t>+3.09%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>328</v>
+        <v>2335</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.69%987,000</t>
+          <t>1.68%148,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>987000</v>
+        <v>148000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:59</t>
+          <t>2026-09-09 19:33:09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2360致茂電子</t>
+          <t>2382廣達電腦</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+1.57%2265</t>
+          <t>+4.27%342</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>+4.27%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2265</v>
+        <v>342</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.63%148,000</t>
+          <t>1.62%987,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>148000</v>
+        <v>987000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:59</t>
+          <t>2026-09-09 19:33:09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,25 +2034,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-0.48%618</t>
+          <t>+3.56%640</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>+3.56%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>618</v>
+        <v>640</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.61%526,000</t>
+          <t>1.62%526,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:59</t>
+          <t>2026-09-09 19:33:09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+1.19%68.2</t>
+          <t>-2.35%66.6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+1.19%</t>
+          <t>-2.35%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>68.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.51%4,525,000</t>
+          <t>1.54%4,525,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:59</t>
+          <t>2026-09-09 19:33:09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6274台燿科技</t>
+          <t>2884玉山金融控股</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.82%1345</t>
+          <t>-2.85%44.25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1345</v>
+        <v>44.25</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.41%209,000</t>
+          <t>1.44%6,340,622</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>209000</v>
+        <v>6340622</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:59</t>
+          <t>2026-09-09 19:33:09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2884玉山金融控股</t>
+          <t>6274台燿科技</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+4.59%45.55</t>
+          <t>0%1345</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+4.59%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>45.55</v>
+        <v>1345</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.36%6,340,622</t>
+          <t>1.40%209,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>6340622</v>
+        <v>209000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:59</t>
+          <t>2026-09-09 19:33:09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-2.06%357</t>
+          <t>-2.1%349.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.06%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>357</v>
+        <v>349.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.25%694,000</t>
+          <t>1.24%694,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:00</t>
+          <t>2026-09-09 19:33:11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,25 +2339,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.58%510</t>
+          <t>+2.55%523</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>+2.55%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.22%482,000</t>
+          <t>1.23%482,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:00</t>
+          <t>2026-09-09 19:33:11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,25 +2400,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+0.8%505</t>
+          <t>-0.59%502</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+0.8%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.14%461,000</t>
+          <t>1.16%461,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:00</t>
+          <t>2026-09-09 19:33:11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0%71.7</t>
+          <t>+1.67%72.9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.67%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>71.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.11%3,124,500</t>
+          <t>1.12%3,124,500</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:00</t>
+          <t>2026-09-09 19:33:11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.21%1225</t>
+          <t>+9.8%1345</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>+9.8%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1225</v>
+        <v>1345</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:00</t>
+          <t>2026-09-09 19:33:11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-1.56%189.5</t>
+          <t>+1.06%191.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>+1.06%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>189.5</v>
+        <v>191.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:00</t>
+          <t>2026-09-09 19:33:11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,25 +2644,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-2.38%1025</t>
+          <t>+8.29%1110</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>+8.29%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1025</v>
+        <v>1110</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.05%203,000</t>
+          <t>1.04%203,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:00</t>
+          <t>2026-09-09 19:33:11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-5.33%186.5</t>
+          <t>+1.34%189</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-5.33%</t>
+          <t>+1.34%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>186.5</v>
+        <v>189</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.01%1,041,000</t>
+          <t>0.97%1,041,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:00</t>
+          <t>2026-09-09 19:33:11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,25 +2761,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>8210勤誠興業</t>
+          <t>3293鈊象電子</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-3.2%907</t>
+          <t>0%708</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>907</v>
+        <v>708</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.89%193,000</t>
+          <t>0.89%252,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2788,11 +2788,11 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>193000</v>
+        <v>252000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:00</t>
+          <t>2026-09-09 19:33:11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3293鈊象電子</t>
+          <t>8210勤誠興業</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-0.28%708</t>
+          <t>+0.99%916</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>708</v>
+        <v>916</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.88%252,000</t>
+          <t>0.87%193,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>252000</v>
+        <v>193000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:00</t>
+          <t>2026-09-09 19:33:11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-2.4%6500</t>
+          <t>+5.69%6870</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>+5.69%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6500</v>
+        <v>6870</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.85%26,000</t>
+          <t>0.84%26,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:00</t>
+          <t>2026-09-09 19:33:11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-1.83%484</t>
+          <t>+5.17%509</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-1.83%</t>
+          <t>+5.17%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>484</v>
+        <v>509</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.84%345,000</t>
+          <t>0.83%345,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:00</t>
+          <t>2026-09-09 19:33:11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.6%800</t>
+          <t>+1.5%812</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>+1.5%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:00</t>
+          <t>2026-09-09 19:33:11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.88%225</t>
+          <t>+3.56%233</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+3.56%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:00</t>
+          <t>2026-09-09 19:33:11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>3529力旺電子</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-4.86%2155</t>
+          <t>-1.59%2780</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-4.86%</t>
+          <t>-1.59%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2155</v>
+        <v>2780</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.60%54,000</t>
+          <t>0.62%44,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>54000</v>
+        <v>44000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:00</t>
+          <t>2026-09-09 19:33:11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,38 +3188,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3529力旺電子</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+9.92%2825</t>
+          <t>+6.5%2295</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+9.92%</t>
+          <t>+6.5%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2825</v>
+        <v>2295</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.56%44,000</t>
+          <t>0.58%54,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.58%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>44000</v>
+        <v>54000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:01</t>
+          <t>2026-09-09 19:33:12</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,25 +3249,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3026禾伸堂企業</t>
+          <t>6831邁科科技</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-3.11%747</t>
+          <t>+2.68%575</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-3.11%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>747</v>
+        <v>575</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.51%134,000</t>
+          <t>0.51%182,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3276,11 +3276,11 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>134000</v>
+        <v>182000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:01</t>
+          <t>2026-09-09 19:33:12</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,38 +3310,38 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6831邁科科技</t>
+          <t>3026禾伸堂企業</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-1.41%560</t>
+          <t>+1.47%758</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-1.41%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>560</v>
+        <v>758</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.51%182,000</t>
+          <t>0.50%134,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>182000</v>
+        <v>134000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:01</t>
+          <t>2026-09-09 19:33:12</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,38 +3371,38 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>3665貿聯控股（BizLink Holding In</t>
+          <t>6442光紅建聖</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-6.52%1935</t>
+          <t>+0.29%1700</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-6.52%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1935</v>
+        <v>1700</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.33%32,336</t>
+          <t>0.32%38,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>32336</v>
+        <v>38000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:01</t>
+          <t>2026-09-09 19:33:12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,38 +3432,38 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6442光紅建聖</t>
+          <t>3665貿聯控股（BizLink Holding In</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.29%1695</t>
+          <t>+2.07%1975</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+2.07%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1695</v>
+        <v>1975</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.32%38,000</t>
+          <t>0.31%32,336</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>38000</v>
+        <v>32336</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:01</t>
+          <t>2026-09-09 19:33:12</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,25 +3498,25 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-4.42%1620</t>
+          <t>+0.31%1625</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-4.42%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1620</v>
+        <v>1625</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.29%35,000</t>
+          <t>0.28%35,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:08</t>
+          <t>2026-09-09 22:36:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:08</t>
+          <t>2026-09-09 22:36:31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:08</t>
+          <t>2026-09-09 22:36:31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:08</t>
+          <t>2026-09-09 22:36:31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:08</t>
+          <t>2026-09-09 22:36:31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:08</t>
+          <t>2026-09-09 22:36:31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:08</t>
+          <t>2026-09-09 22:36:31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:08</t>
+          <t>2026-09-09 22:36:31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:08</t>
+          <t>2026-09-09 22:36:31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:08</t>
+          <t>2026-09-09 22:36:31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:08</t>
+          <t>2026-09-09 22:36:31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:08</t>
+          <t>2026-09-09 22:36:31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:08</t>
+          <t>2026-09-09 22:36:31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:08</t>
+          <t>2026-09-09 22:36:31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:08</t>
+          <t>2026-09-09 22:36:31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:09</t>
+          <t>2026-09-09 22:36:33</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:09</t>
+          <t>2026-09-09 22:36:33</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:09</t>
+          <t>2026-09-09 22:36:33</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:09</t>
+          <t>2026-09-09 22:36:33</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:09</t>
+          <t>2026-09-09 22:36:33</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:09</t>
+          <t>2026-09-09 22:36:33</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:09</t>
+          <t>2026-09-09 22:36:33</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:09</t>
+          <t>2026-09-09 22:36:33</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:09</t>
+          <t>2026-09-09 22:36:33</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:09</t>
+          <t>2026-09-09 22:36:33</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:09</t>
+          <t>2026-09-09 22:36:33</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:09</t>
+          <t>2026-09-09 22:36:33</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:09</t>
+          <t>2026-09-09 22:36:33</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:09</t>
+          <t>2026-09-09 22:36:33</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:09</t>
+          <t>2026-09-09 22:36:33</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:11</t>
+          <t>2026-09-09 22:36:34</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:11</t>
+          <t>2026-09-09 22:36:34</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:11</t>
+          <t>2026-09-09 22:36:34</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:11</t>
+          <t>2026-09-09 22:36:34</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:11</t>
+          <t>2026-09-09 22:36:34</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:11</t>
+          <t>2026-09-09 22:36:34</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:11</t>
+          <t>2026-09-09 22:36:34</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:11</t>
+          <t>2026-09-09 22:36:34</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:11</t>
+          <t>2026-09-09 22:36:34</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:11</t>
+          <t>2026-09-09 22:36:34</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:11</t>
+          <t>2026-09-09 22:36:34</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:11</t>
+          <t>2026-09-09 22:36:34</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:11</t>
+          <t>2026-09-09 22:36:34</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:11</t>
+          <t>2026-09-09 22:36:34</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:11</t>
+          <t>2026-09-09 22:36:34</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:12</t>
+          <t>2026-09-09 22:36:35</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:12</t>
+          <t>2026-09-09 22:36:35</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:12</t>
+          <t>2026-09-09 22:36:35</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:12</t>
+          <t>2026-09-09 22:36:35</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:12</t>
+          <t>2026-09-09 22:36:35</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:31</t>
+          <t>2026-09-09 22:47:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:31</t>
+          <t>2026-09-09 22:47:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:31</t>
+          <t>2026-09-09 22:47:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:31</t>
+          <t>2026-09-09 22:47:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:31</t>
+          <t>2026-09-09 22:47:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:31</t>
+          <t>2026-09-09 22:47:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:31</t>
+          <t>2026-09-09 22:47:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:31</t>
+          <t>2026-09-09 22:47:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:31</t>
+          <t>2026-09-09 22:47:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:31</t>
+          <t>2026-09-09 22:47:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:31</t>
+          <t>2026-09-09 22:47:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:31</t>
+          <t>2026-09-09 22:47:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:31</t>
+          <t>2026-09-09 22:47:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:31</t>
+          <t>2026-09-09 22:47:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:31</t>
+          <t>2026-09-09 22:47:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:33</t>
+          <t>2026-09-09 22:47:38</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:33</t>
+          <t>2026-09-09 22:47:38</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:33</t>
+          <t>2026-09-09 22:47:38</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:33</t>
+          <t>2026-09-09 22:47:38</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:33</t>
+          <t>2026-09-09 22:47:38</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:33</t>
+          <t>2026-09-09 22:47:38</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:33</t>
+          <t>2026-09-09 22:47:38</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:33</t>
+          <t>2026-09-09 22:47:38</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:33</t>
+          <t>2026-09-09 22:47:38</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:33</t>
+          <t>2026-09-09 22:47:38</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:33</t>
+          <t>2026-09-09 22:47:38</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:33</t>
+          <t>2026-09-09 22:47:38</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:33</t>
+          <t>2026-09-09 22:47:38</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:33</t>
+          <t>2026-09-09 22:47:38</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:33</t>
+          <t>2026-09-09 22:47:38</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:34</t>
+          <t>2026-09-09 22:47:39</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:34</t>
+          <t>2026-09-09 22:47:39</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:34</t>
+          <t>2026-09-09 22:47:39</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:34</t>
+          <t>2026-09-09 22:47:39</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:34</t>
+          <t>2026-09-09 22:47:39</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:34</t>
+          <t>2026-09-09 22:47:39</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:34</t>
+          <t>2026-09-09 22:47:39</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:34</t>
+          <t>2026-09-09 22:47:39</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:34</t>
+          <t>2026-09-09 22:47:39</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:34</t>
+          <t>2026-09-09 22:47:39</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:34</t>
+          <t>2026-09-09 22:47:39</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:34</t>
+          <t>2026-09-09 22:47:39</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:34</t>
+          <t>2026-09-09 22:47:39</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:34</t>
+          <t>2026-09-09 22:47:39</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:34</t>
+          <t>2026-09-09 22:47:39</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:35</t>
+          <t>2026-09-09 22:47:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:35</t>
+          <t>2026-09-09 22:47:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:35</t>
+          <t>2026-09-09 22:47:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:35</t>
+          <t>2026-09-09 22:47:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:35</t>
+          <t>2026-09-09 22:47:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:37</t>
+          <t>2026-09-09 23:09:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:37</t>
+          <t>2026-09-09 23:09:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:37</t>
+          <t>2026-09-09 23:09:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:37</t>
+          <t>2026-09-09 23:09:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:37</t>
+          <t>2026-09-09 23:09:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:37</t>
+          <t>2026-09-09 23:09:32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:37</t>
+          <t>2026-09-09 23:09:32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:37</t>
+          <t>2026-09-09 23:09:32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:37</t>
+          <t>2026-09-09 23:09:32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:37</t>
+          <t>2026-09-09 23:09:32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:37</t>
+          <t>2026-09-09 23:09:32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:37</t>
+          <t>2026-09-09 23:09:32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:37</t>
+          <t>2026-09-09 23:09:32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:37</t>
+          <t>2026-09-09 23:09:32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:37</t>
+          <t>2026-09-09 23:09:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:38</t>
+          <t>2026-09-09 23:09:33</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:38</t>
+          <t>2026-09-09 23:09:33</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:38</t>
+          <t>2026-09-09 23:09:33</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:38</t>
+          <t>2026-09-09 23:09:33</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:38</t>
+          <t>2026-09-09 23:09:33</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:38</t>
+          <t>2026-09-09 23:09:33</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:38</t>
+          <t>2026-09-09 23:09:33</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:38</t>
+          <t>2026-09-09 23:09:33</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:38</t>
+          <t>2026-09-09 23:09:33</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:38</t>
+          <t>2026-09-09 23:09:33</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:38</t>
+          <t>2026-09-09 23:09:33</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:38</t>
+          <t>2026-09-09 23:09:33</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:38</t>
+          <t>2026-09-09 23:09:33</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:38</t>
+          <t>2026-09-09 23:09:33</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:38</t>
+          <t>2026-09-09 23:09:33</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:39</t>
+          <t>2026-09-09 23:09:35</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:39</t>
+          <t>2026-09-09 23:09:35</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:39</t>
+          <t>2026-09-09 23:09:35</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:39</t>
+          <t>2026-09-09 23:09:35</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:39</t>
+          <t>2026-09-09 23:09:35</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:39</t>
+          <t>2026-09-09 23:09:35</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:39</t>
+          <t>2026-09-09 23:09:35</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:39</t>
+          <t>2026-09-09 23:09:35</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:39</t>
+          <t>2026-09-09 23:09:35</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:39</t>
+          <t>2026-09-09 23:09:35</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:39</t>
+          <t>2026-09-09 23:09:35</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:39</t>
+          <t>2026-09-09 23:09:35</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:39</t>
+          <t>2026-09-09 23:09:35</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:39</t>
+          <t>2026-09-09 23:09:35</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:39</t>
+          <t>2026-09-09 23:09:35</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:41</t>
+          <t>2026-09-09 23:09:36</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:41</t>
+          <t>2026-09-09 23:09:36</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:41</t>
+          <t>2026-09-09 23:09:36</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:41</t>
+          <t>2026-09-09 23:09:36</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:41</t>
+          <t>2026-09-09 23:09:36</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
